--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.2).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.2).xlsx
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>1.2k</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
